--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6771-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6771-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7423727-D34C-4829-9A2A-074D72497BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34753BC1-CAC5-4CEF-BA29-32A0CBBE4C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4FED85C7-DCA8-4184-9E74-33A5BD13741A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{21ECDEFC-6A80-4C98-AB06-D085DC93D525}"/>
   </bookViews>
   <sheets>
     <sheet name="6771-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1439,18 +1439,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2220617-EF7C-4976-AD27-C636DEAE8191}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C94B132-2157-4278-BD41-A61B5E463316}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1604,7 +1604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2022</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2021</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2020</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
         <v>32</v>
       </c>
